--- a/site/downloads/herd-record-template.xlsx
+++ b/site/downloads/herd-record-template.xlsx
@@ -612,10 +612,11 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Herd record template: Lone Star Exotics Hub (free)</t>
+          <t>Herd record template: Exotic Ranch &amp; Wildlife Network (free)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
